--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.60238</v>
+        <v>16.79076</v>
       </c>
       <c r="D2" t="n">
-        <v>16.57143</v>
+        <v>16.32691</v>
       </c>
       <c r="E2" t="n">
-        <v>16.88111</v>
+        <v>16.61194</v>
       </c>
       <c r="F2" t="n">
-        <v>41.65488</v>
+        <v>42.15795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05036</v>
+        <v>0.05047</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84686</v>
+        <v>1.79901</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.68455</v>
+        <v>16.85584</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35695</v>
+        <v>16.52116</v>
       </c>
       <c r="E3" t="n">
-        <v>16.33662</v>
+        <v>16.73921</v>
       </c>
       <c r="F3" t="n">
-        <v>41.82933</v>
+        <v>42.78183</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05086</v>
+        <v>0.05087</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8051</v>
+        <v>1.82153</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.53411</v>
+        <v>16.69318</v>
       </c>
       <c r="D4" t="n">
-        <v>16.47213</v>
+        <v>15.99229</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63773</v>
+        <v>16.49879</v>
       </c>
       <c r="F4" t="n">
-        <v>43.41474</v>
+        <v>42.58157</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05067</v>
+        <v>0.05077</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8113</v>
+        <v>1.80785</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.65708</v>
+        <v>16.55753</v>
       </c>
       <c r="D6" t="n">
-        <v>15.53529</v>
+        <v>15.82696</v>
       </c>
       <c r="E6" t="n">
-        <v>16.17375</v>
+        <v>16.45112</v>
       </c>
       <c r="F6" t="n">
-        <v>21.73116</v>
+        <v>21.80559</v>
       </c>
       <c r="G6" t="n">
-        <v>34.57615</v>
+        <v>33.49938</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84904</v>
+        <v>16.38536</v>
       </c>
       <c r="D7" t="n">
-        <v>15.66599</v>
+        <v>16.02173</v>
       </c>
       <c r="E7" t="n">
-        <v>16.25319</v>
+        <v>16.08078</v>
       </c>
       <c r="F7" t="n">
-        <v>21.60468</v>
+        <v>21.43981</v>
       </c>
       <c r="G7" t="n">
-        <v>34.67045</v>
+        <v>33.68421</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.73322</v>
+        <v>16.69913</v>
       </c>
       <c r="D8" t="n">
-        <v>15.96431</v>
+        <v>15.85621</v>
       </c>
       <c r="E8" t="n">
-        <v>16.01147</v>
+        <v>16.18427</v>
       </c>
       <c r="F8" t="n">
-        <v>21.67761</v>
+        <v>21.87284</v>
       </c>
       <c r="G8" t="n">
-        <v>33.42009</v>
+        <v>33.87115</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60485</v>
+        <v>0.60536</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10885</v>
+        <v>1.11257</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6142</v>
+        <v>0.60659</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11792</v>
+        <v>1.09871</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60251</v>
+        <v>0.60678</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10087</v>
+        <v>1.11517</v>
       </c>
     </row>
   </sheetData>
